--- a/_ForDRA/BVSimulationFiles/59.xlsx
+++ b/_ForDRA/BVSimulationFiles/59.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.002060301507537688</v>
+        <v>0.04120603015075376</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001984413640413067</v>
+        <v>0.03968827280826134</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001911320979890807</v>
+        <v>0.03822641959781614</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001840920569065596</v>
+        <v>0.03681841138131192</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001773113243282878</v>
+        <v>0.03546226486565756</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001707803490457443</v>
+        <v>0.03415606980914886</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001644899316536953</v>
+        <v>0.03289798633073906</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001584312115920903</v>
+        <v>0.03168624231841806</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001525956546652489</v>
+        <v>0.03051913093304978</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001469750410207582</v>
+        <v>0.02939500820415164</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00141561453571148</v>
+        <v>0.0283122907142296</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001363472668420345</v>
+        <v>0.0272694533684069</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001313251362310252</v>
+        <v>0.02626502724620504</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001264879876622541</v>
+        <v>0.02529759753245082</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001218290076219756</v>
+        <v>0.02436580152439512</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001173416335611808</v>
+        <v>0.02346832671223616</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001130195446517186</v>
+        <v>0.02260390893034372</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001088566528828992</v>
+        <v>0.02177133057657984</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001048470944860405</v>
+        <v>0.0209694188972081</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001009852216748769</v>
+        <v>0.02019704433497538</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002060301507537688</v>
+        <v>0.04120603015075376</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001984413640413067</v>
+        <v>0.03968827280826134</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001911320979890807</v>
+        <v>0.03822641959781614</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001840920569065596</v>
+        <v>0.03681841138131192</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001773113243282878</v>
+        <v>0.03546226486565756</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001707803490457443</v>
+        <v>0.03415606980914886</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001644899316536953</v>
+        <v>0.03289798633073906</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001584312115920903</v>
+        <v>0.03168624231841806</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001525956546652489</v>
+        <v>0.03051913093304978</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001469750410207582</v>
+        <v>0.02939500820415164</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00141561453571148</v>
+        <v>0.0283122907142296</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001363472668420345</v>
+        <v>0.0272694533684069</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001313251362310252</v>
+        <v>0.02626502724620504</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001264879876622541</v>
+        <v>0.02529759753245082</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001218290076219756</v>
+        <v>0.02436580152439512</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001173416335611808</v>
+        <v>0.02346832671223616</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001130195446517186</v>
+        <v>0.02260390893034372</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001088566528828992</v>
+        <v>0.02177133057657984</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001048470944860405</v>
+        <v>0.0209694188972081</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001009852216748769</v>
+        <v>0.02019704433497538</v>
       </c>
     </row>
   </sheetData>
